--- a/nfl_stats.xlsx
+++ b/nfl_stats.xlsx
@@ -1,13 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NFL_Stats" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFL_Stats" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +24,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,11 +58,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,1113 +429,3012 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Team_Abbr</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>QB_Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>EPA_Pass_Off</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPA_Rush_Off</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPA_Pass_Def</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPA_Rush_Def</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Success_Rate_Off</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Success_Rate_Def</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Pace_Sec</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Drives_Game</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RedZone_TD_Pct</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Pressure_Pct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Def_RZ_Stop_Pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Dome</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Cold_Weather_Drop</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>RB1_TD_Rate</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>WR1_TD_Rate</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TE1_TD_Rate</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>QB_Rush_TD_Rate</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Pass_Rate</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HFA_Mod</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>RB1_Nombre</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>WR1_Nombre</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>TE1_Nombre</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>P. Mahomes</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>0.113</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>0.134</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>-0.136</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>-0.05</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.493</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>0.384</v>
       </c>
-      <c r="I2" t="n">
-        <v>30.22</v>
+      <c r="I2" s="2" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Kansas City Chiefs</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>K. Walker III</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>R. Rice</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>T. Kelce</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>B. Purdy</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>0.236</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>0.092</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>0.027</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="2" t="n">
         <v>-0.042</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="2" t="n">
         <v>0.528</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.435</v>
       </c>
-      <c r="I3" t="n">
-        <v>32.75</v>
+      <c r="I3" s="2" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco 49ers</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>C. McCaffrey</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>M. Evans</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>G. Kittle</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BUF</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>J. Allen</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>0.247</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>0.156</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>0.182</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.058</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="2" t="n">
         <v>0.489</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.474</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>28.66</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Buffalo Bills</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>J. Cook III</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>D.J. Moore</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>D. Kincaid</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>T. Huntley</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>0.206</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>0.019</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>-0.028</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="2" t="n">
         <v>-0.033</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="2" t="n">
         <v>0.479</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.417</v>
       </c>
-      <c r="I5" t="n">
-        <v>31.99</v>
+      <c r="I5" s="2" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Baltimore Ravens</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>D. Henry</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Z. Flowers</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>M. Andrews</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>J. Goff</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2" t="n">
         <v>-0.005</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>0.222</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="2" t="n">
         <v>0.051</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.491</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.476</v>
       </c>
-      <c r="I6" t="n">
-        <v>28.86</v>
+      <c r="I6" s="2" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Detroit Lions</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>J. Gibbs</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>A. St. Brown</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>S. LaPorta</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>DAL</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>D. Prescott</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>0.125</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="2" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="2" t="n">
         <v>0.468</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.493</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="2" t="n">
         <v>28.19</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Dallas Cowboys</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>J. Williams</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>C. Lamb</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>J. Ferguson</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>T. McKee</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>-0.197</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="2" t="n">
         <v>-0.147</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="2" t="n">
         <v>0.121</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="2" t="n">
         <v>0.024</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="2" t="n">
         <v>0.365</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.447</v>
       </c>
-      <c r="I8" t="n">
-        <v>31.03</v>
+      <c r="I8" s="2" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Philadelphia Eagles</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>S. Barkley</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>D. Smith</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>D. Goedert</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>NE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>D. Maye</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>0.151</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="2" t="n">
         <v>-0.045</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.038</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.004</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.452</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.438</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="2" t="n">
         <v>29.74</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>New England Patriots</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>R. Stevenson</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>H. Henry</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>C.J. Stroud</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>0.125</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="2" t="n">
         <v>-0.149</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="2" t="n">
         <v>0.007</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="2" t="n">
         <v>0.432</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="2" t="n">
         <v>0.414</v>
       </c>
-      <c r="I10" t="n">
-        <v>29.98</v>
+      <c r="I10" s="2" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Houston Texans</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D. Montgomery</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>N. Collins</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>D. Schultz</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>J. Love</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>0.115</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="2" t="n">
         <v>-0.265</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="2" t="n">
         <v>-0.092</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="2" t="n">
         <v>0.034</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="2" t="n">
         <v>0.402</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.438</v>
       </c>
-      <c r="I11" t="n">
-        <v>29.1</v>
+      <c r="I11" s="2" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Green Bay Packers</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>J. Jacobs</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>C. Watson</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>T. Kraft</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>J. Burrow</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>0.139</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="2" t="n">
         <v>-0.048</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="2" t="n">
         <v>-0.053</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="2" t="n">
         <v>0.002</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="2" t="n">
         <v>0.471</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="I12" t="n">
-        <v>30.14</v>
+      <c r="I12" s="2" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Cincinnati Bengals</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>C. Brown</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>J. Chase</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>M. Gesicki</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>M. Willis</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>-0.225</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="2" t="n">
         <v>0.005</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>0.154</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="2" t="n">
         <v>0.049</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="2" t="n">
         <v>0.376</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="2" t="n">
         <v>0.486</v>
       </c>
-      <c r="I13" t="n">
-        <v>29.98</v>
+      <c r="I13" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Miami Dolphins</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>O. Gordon II</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>M. Washington</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>G. Dulcich</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LAR</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>M. Stafford</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>0.074</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="2" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="2" t="n">
         <v>-0.063</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="2" t="n">
         <v>0.042</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="2" t="n">
         <v>0.473</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.436</v>
       </c>
-      <c r="I14" t="n">
-        <v>28.21</v>
+      <c r="I14" s="2" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Los Angeles Rams</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>K. Williams</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>P. Nacua</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>C. Parkinson</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>K. Murray</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>-0.08500000000000001</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="2" t="n">
         <v>-0.114</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="2" t="n">
         <v>-0.288</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="2" t="n">
         <v>-0.102</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="2" t="n">
         <v>0.359</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="2" t="n">
         <v>0.332</v>
       </c>
-      <c r="I15" t="n">
-        <v>29.93</v>
+      <c r="I15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Minnesota Vikings</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>A. Jones</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>J. Jefferson</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>T.J. Hockenson</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>NYJ</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>G. Smith</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>0.061</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="2" t="n">
         <v>-0.14</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="2" t="n">
         <v>-0.063</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="2" t="n">
         <v>-0.031</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="2" t="n">
         <v>0.438</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="2" t="n">
         <v>0.441</v>
       </c>
-      <c r="I16" t="n">
-        <v>32.06</v>
+      <c r="I16" s="2" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>New York Jets</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B. Hall</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>G. Wilson</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>M. Taylor</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>D. Watson</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>-0.037</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="2" t="n">
         <v>-0.153</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="2" t="n">
         <v>-0.034</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="2" t="n">
         <v>-0.025</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="2" t="n">
         <v>0.398</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="2" t="n">
         <v>0.418</v>
       </c>
-      <c r="I17" t="n">
-        <v>29.24</v>
+      <c r="I17" s="2" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Cleveland Browns</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Q. Judkins</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>D. Boston</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>H. Fannin Jr.</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>A. Rodgers</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2" t="n">
         <v>-0.136</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="2" t="n">
         <v>0.048</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="2" t="n">
         <v>-0.079</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="2" t="n">
         <v>-0.033</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="2" t="n">
         <v>0.408</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="2" t="n">
         <v>0.415</v>
       </c>
-      <c r="I18" t="n">
-        <v>30.13</v>
+      <c r="I18" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Pittsburgh Steelers</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>J. Warren</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>D.K. Metcalf</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>D. Washington</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>M. Penix Jr.</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="2" t="n">
         <v>-0.131</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="2" t="n">
         <v>0.023</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="2" t="n">
         <v>-0.029</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="2" t="n">
         <v>-0.007</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="2" t="n">
         <v>0.443</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="2" t="n">
         <v>0.419</v>
       </c>
-      <c r="I19" t="n">
-        <v>32.13</v>
+      <c r="I19" s="2" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta Falcons</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B. Robinson</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>D. London</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>K. Pitts</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>CHI</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>C. Williams</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="2" t="n">
         <v>0.106</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="2" t="n">
         <v>-0.014</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="2" t="n">
         <v>0.007</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="2" t="n">
         <v>0.467</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="2" t="n">
         <v>0.416</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="2" t="n">
         <v>28.83</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Chicago Bears</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D. Swift</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>R. Odunze</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>C. Loveland</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>JAX</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>T. Lawrence</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="2" t="n">
         <v>0.275</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="2" t="n">
         <v>0.011</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="2" t="n">
         <v>-0.056</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="2" t="n">
         <v>-0.017</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="2" t="n">
         <v>0.479</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="2" t="n">
         <v>0.427</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="2" t="n">
         <v>29.67</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Jacksonville Jaguars</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B. Tuten</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>P. Washington</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>B. Strange</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>D. Jones</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>-0.145</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="2" t="n">
         <v>0.056</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="2" t="n">
         <v>0.042</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="2" t="n">
         <v>0.421</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="2" t="n">
         <v>0.436</v>
       </c>
-      <c r="I22" t="n">
-        <v>29.62</v>
+      <c r="I22" s="2" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Indianapolis Colts</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>J. Taylor</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>J. Downs</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>T. Warren</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>S. Darnold</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="2" t="n">
         <v>0.007</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="2" t="n">
         <v>-0.185</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="2" t="n">
         <v>-0.191</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="2" t="n">
         <v>-0.045</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="2" t="n">
         <v>0.411</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="2" t="n">
         <v>0.368</v>
       </c>
-      <c r="I23" t="n">
-        <v>31.57</v>
+      <c r="I23" s="2" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>E. Wilson</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>J. Smith-Njigba</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>A. Barner</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>B. Mayfield</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="2" t="n">
         <v>-0.296</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="2" t="n">
         <v>0.028</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="2" t="n">
         <v>-0.12</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="2" t="n">
         <v>-0.048</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="2" t="n">
         <v>0.388</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="2" t="n">
         <v>0.407</v>
       </c>
-      <c r="I24" t="n">
-        <v>32.64</v>
+      <c r="I24" s="2" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Tampa Bay Buccaneers</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B. Irving</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>E. Egbuka</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>C. Otton</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>J. Daniels</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="2" t="n">
         <v>-0.033</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="2" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="2" t="n">
         <v>0.046</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="2" t="n">
         <v>0.411</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="2" t="n">
         <v>0.476</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="2" t="n">
         <v>28.45</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Washington Commanders</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>R. White</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>S. Diggs</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>C. Okonkwo</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>ARI</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>J. Brissett</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="2" t="n">
         <v>0.005</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="2" t="n">
         <v>-0.117</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="2" t="n">
         <v>0.097</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="2" t="n">
         <v>0.056</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="2" t="n">
         <v>0.464</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="2" t="n">
         <v>0.446</v>
       </c>
-      <c r="I26" t="n">
-        <v>30.82</v>
+      <c r="I26" s="2" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Arizona Cardinals</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>J. Love</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>M. Wilson</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>T. McBride</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>J. Herbert</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="2" t="n">
         <v>-0.268</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="2" t="n">
         <v>-0.174</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="2" t="n">
         <v>-0.054</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="2" t="n">
         <v>-0.021</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="2" t="n">
         <v>0.359</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="2" t="n">
         <v>0.435</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="2" t="n">
         <v>28.74</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Los Angeles Chargers</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>O. Hampton</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>L. McConkey</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>C. Kolar</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>T. Shough</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="2" t="n">
         <v>-0.036</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="2" t="n">
         <v>-0.074</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="2" t="n">
         <v>0.096</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="2" t="n">
         <v>0.034</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="2" t="n">
         <v>0.416</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="2" t="n">
         <v>0.492</v>
       </c>
-      <c r="I28" t="n">
-        <v>27.15</v>
+      <c r="I28" s="2" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>New Orleans Saints</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>A. Kamara</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>C. Olave</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>J. Johnson</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>K. Cousins</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>0.182</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="2" t="n">
         <v>-0.233</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="2" t="n">
         <v>0.039</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="2" t="n">
         <v>0.018</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="2" t="n">
         <v>0.426</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="2" t="n">
         <v>0.454</v>
       </c>
-      <c r="I29" t="n">
-        <v>28.8</v>
+      <c r="I29" s="2" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Las Vegas Raiders</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>A. Jeanty</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>T. Tucker</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>B. Bowers</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>B. Nix</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="2" t="n">
         <v>-0.075</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="2" t="n">
         <v>-0.08500000000000001</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="2" t="n">
         <v>-0.055</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="2" t="n">
         <v>-0.02</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="2" t="n">
         <v>0.403</v>
       </c>
-      <c r="I30" t="n">
-        <v>29.33</v>
+      <c r="I30" s="2" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Denver Broncos</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>J. Waddle</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>E. Engram</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>TEN</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>C. Ward</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="2" t="n">
         <v>-0.198</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="2" t="n">
         <v>-0.078</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="2" t="n">
         <v>0.06</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="2" t="n">
         <v>0.013</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" s="2" t="n">
         <v>0.403</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="2" t="n">
         <v>0.433</v>
       </c>
-      <c r="I31" t="n">
-        <v>28.4</v>
+      <c r="I31" s="2" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Tennessee Titans</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>T. Pollard</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>C. Tate</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>G. Helm</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>NYG</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>J.J. McCarthy</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="2" t="n">
         <v>0.033</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="2" t="n">
         <v>-0.106</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="2" t="n">
         <v>0.016</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="2" t="n">
         <v>0.076</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" s="2" t="n">
         <v>0.423</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="2" t="n">
         <v>0.439</v>
       </c>
-      <c r="I32" t="n">
-        <v>29.79</v>
+      <c r="I32" s="2" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>New York Giants</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>C. Skattebo</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>M. Nabers</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>I. Likely</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>CAR</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>B. Young</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="2" t="n">
         <v>0.186</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="2" t="n">
         <v>-0.005</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="2" t="n">
         <v>0.019</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="2" t="n">
         <v>0.019</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="2" t="n">
         <v>0.441</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="2" t="n">
         <v>0.424</v>
       </c>
-      <c r="I33" t="n">
-        <v>25.56</v>
+      <c r="I33" s="2" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Carolina Panthers</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>C. Hubbard</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>T. McMillan</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>T. Tremble</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>